--- a/public/modelo-atletas-rumia.xlsx
+++ b/public/modelo-atletas-rumia.xlsx
@@ -397,12 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -413,9 +414,12 @@
         <v>Número</v>
       </c>
       <c r="C1" t="str">
+        <v>Data de nascimento</v>
+      </c>
+      <c r="D1" t="str">
         <v>Ano de nascimento</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Posição</v>
       </c>
     </row>
@@ -427,9 +431,12 @@
         <v>7</v>
       </c>
       <c r="C2" t="str">
+        <v>14/03/2008</v>
+      </c>
+      <c r="D2" t="str">
         <v>2008</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>Distribuidor</v>
       </c>
     </row>
@@ -441,9 +448,12 @@
         <v>12</v>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
         <v>2009</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Central</v>
       </c>
     </row>
@@ -455,9 +465,12 @@
         <v>5</v>
       </c>
       <c r="C4" t="str">
+        <v>02/11/2008</v>
+      </c>
+      <c r="D4" t="str">
         <v>2008</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>Líbero</v>
       </c>
     </row>
@@ -469,15 +482,18 @@
         <v>9</v>
       </c>
       <c r="C5" t="str">
+        <v>27/06/2010</v>
+      </c>
+      <c r="D5" t="str">
         <v>2010</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>Oposto</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>